--- a/residentlistbylandlord.xlsx
+++ b/residentlistbylandlord.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="7"/>
@@ -474,22 +474,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t xml:space="preserve">Ademoye </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>Temitayo</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2 Adeogun Street</t>
+          <t>4 Martins Street</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2348067136212</t>
         </is>
       </c>
     </row>
@@ -504,22 +504,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dare</t>
+          <t>Adeniyi</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Adeogun</t>
+          <t xml:space="preserve">Solomon </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2 Adeogun Street</t>
+          <t>4 Martins Street</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2348062105535</t>
+          <t>2348067155887</t>
         </is>
       </c>
     </row>
@@ -534,22 +534,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Bish</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>Bolaji</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2 Adeogun Street</t>
+          <t>4 Martins Street</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2347064439966</t>
+          <t>2349032346583</t>
         </is>
       </c>
     </row>
@@ -564,22 +564,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Enaholo</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>David</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2 Adeogun Street</t>
+          <t>4 Martins Street</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2348134694901</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iya Daniel</t>
+          <t>Gift</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -604,372 +604,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2 Adeogun Street</t>
+          <t>4 Martins Street</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Mrs</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Iya Pelumi</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>na</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2 Adeogun Street</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Mr</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Jimoh</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Koulete</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2 Adeogun Street</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2349132223243</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Mr</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>John</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>na</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2 Adeogun Street</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Mr</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>na</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2 Adeogun Street</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Mr</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Kayode</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>na</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2 Adeogun Street</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Mr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Korede</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>na</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2 Adeogun Street</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Mr</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ola</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>na</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2 Adeogun Street</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Mr</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Peter</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>na</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2 Adeogun Street</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Mr</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Sikiru</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>na</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2 Adeogun Street</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Mr</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Sir Tailor</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>na</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2 Adeogun Street</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2348064658198</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Mr</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Soji</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Adeogun</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2 Adeogun Street</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2348158941240</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Mr</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Solomon</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>na</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2 Adeogun Street</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>2347061533148</t>
         </is>
       </c>
     </row>
